--- a/mau_csv/MAU_02_chon_CLB_muon_thi.xlsx
+++ b/mau_csv/MAU_02_chon_CLB_muon_thi.xlsx
@@ -430,16 +430,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,17 +469,37 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>score_1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>test_club_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>score_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_club_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>score_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_club_4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>score_4</t>
         </is>
       </c>
     </row>
@@ -498,15 +522,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>clb_tienganh</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>clb_amnhac</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,9 +569,17 @@
           <t>clb_tienganh</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,11 +600,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -577,17 +637,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>clb_bongro</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>clb_tienganh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -612,9 +692,17 @@
           <t>clb_mythuat</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -627,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -710,27 +798,69 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>score_1…       Điểm chấm cho CLB cùng SỐ THỨ TỰ: score_1 đi với</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mọi mã CLB phải đã tồn tại. Học sinh có bất kỳ mã sai nào sẽ bị</t>
+          <t xml:space="preserve">               test_club_1, score_2 đi với test_club_2. Ghép theo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bỏ qua TOÀN BỘ kèm cảnh báo — phần mềm không nhập một nửa.</t>
+          <t xml:space="preserve">               số trong tên cột, KHÔNG theo vị trí cột.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               Cột này KHÔNG bắt buộc — bỏ trống thì chấm điểm</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               trong phần mềm như trước. Có điểm sẵn ở đây thì</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               nạp file xong là chạy phân bổ được ngay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mọi mã CLB phải đã tồn tại. Học sinh có bất kỳ mã sai nào sẽ bị</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bỏ qua TOÀN BỘ kèm cảnh báo — phần mềm không nhập một nửa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Xem đầy đủ: mau_csv/HUONG_DAN_CSV.md</t>
         </is>
